--- a/artfynd/A 3819-2024 artfynd.xlsx
+++ b/artfynd/A 3819-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3819-2024 artfynd.xlsx
+++ b/artfynd/A 3819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>406838</v>
+        <v>406835</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588426.2161251551</v>
+        <v>588551</v>
       </c>
       <c r="R2" t="n">
-        <v>6953712.625152527</v>
+        <v>6953627</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2012-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,19 +786,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>406839</v>
+        <v>406836</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588260.4817415955</v>
+        <v>588576</v>
       </c>
       <c r="R3" t="n">
-        <v>6953874.407728415</v>
+        <v>6953596</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,19 +863,9 @@
           <t>2012-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,6 +894,1219 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>406837</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åsen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588598</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6953572</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bäck, äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>406838</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åsen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>588426</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6953713</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bäck, äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>409019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>588570</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6953616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-05-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-05-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bäck, granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>52920329</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, Indalsälven, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>588580</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6953596</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-04-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-04-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>66408694</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, dellokal öster om vägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>588572</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6953597</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66408714</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, dellokal öster om vägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>588569</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6953602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>66408771</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, dellokal öster om vägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>588560</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6953626</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>dellokal öster om vägen, 24 fruktkroppar mellan väg och bäck, 6 fruktkroppar på andra sidan bäcken, sammanlagt 30 stycken</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kerstin Wörler, Helene Öhrling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>84862258</v>
+      </c>
+      <c r="B11" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, dellokal öster om vägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>588561</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6953613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>7 mellan väg o bäck, 2 öster om bäck</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100242520</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pettersbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>588563</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6953622</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fanns en hel del snö kvar längs bäcken, tittar säkert fram fler bombmurklor när det tinat undan.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1449232</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tulpanskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microstoma protractum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kanouse</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åsen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>588551</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6953627</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Bäck, äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>406839</v>
+      </c>
+      <c r="B14" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Åsen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>588260</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6953874</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Bäck, äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3819-2024 artfynd.xlsx
+++ b/artfynd/A 3819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406837</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406838</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/409019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/52920329</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66408694</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66408714</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66408771</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84862258</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100242520</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,8 +2172,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1449232</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>